--- a/SuppXLS/Scen_RES_SHARE_50%_ANNUAL.xlsx
+++ b/SuppXLS/Scen_RES_SHARE_50%_ANNUAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr codeName="Ten_skoroszyt" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aghedupl.sharepoint.com/sites/IPoY45/Shared Documents/CFE/Models/CFE_NL_IND_8760/SuppXLS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasiu\Desktop\PracaMag\Polska\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{E4410707-A914-4723-9547-4430B58C04F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6158FC05-059D-481F-BABF-DDFB61414618}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4A6344-CCBC-45B5-AF8C-6488D2540A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COM_BND" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
   <si>
     <t>Wymagana minimalna produkcja energii elektrycznej z OZE [PJ]</t>
   </si>
@@ -4203,7 +4203,7 @@
     <xf numFmtId="43" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="72" fillId="0" borderId="0" xfId="1112" applyNumberFormat="1" applyFont="1"/>
@@ -4273,6 +4273,9 @@
     </xf>
     <xf numFmtId="190" fontId="25" fillId="47" borderId="22" xfId="1060" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="25" fillId="47" borderId="22" xfId="1060" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2377">
@@ -7514,7 +7517,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Arkusz1"/>
-  <dimension ref="B2:U32"/>
+  <dimension ref="B2:U41"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="1"/>
@@ -7663,8 +7666,8 @@
         <v>1</v>
       </c>
       <c r="G8" s="30">
-        <f>0.5*G25</f>
-        <v>56.52</v>
+        <f>0.5*G39</f>
+        <v>121.85149240264997</v>
       </c>
       <c r="H8" s="30">
         <f>0.5*H25</f>
@@ -7725,7 +7728,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="23" spans="4:11">
+    <row r="23" spans="4:11" ht="13.2" customHeight="1">
       <c r="D23" s="21" t="s">
         <v>24</v>
       </c>
@@ -7886,6 +7889,64 @@
       <c r="E32" s="29"/>
       <c r="F32" s="25" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="4:8">
+      <c r="D36" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="20">
+        <v>2024</v>
+      </c>
+      <c r="F36" s="20">
+        <v>2025</v>
+      </c>
+      <c r="G36" s="20">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="37" spans="4:8" ht="13.2" customHeight="1">
+      <c r="D37" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="34"/>
+      <c r="G37" s="34"/>
+    </row>
+    <row r="38" spans="4:8">
+      <c r="D38" t="s">
+        <v>26</v>
+      </c>
+      <c r="E38">
+        <v>395.99891185173067</v>
+      </c>
+      <c r="F38">
+        <v>392.54883965396471</v>
+      </c>
+      <c r="G38">
+        <v>454.6970151947001</v>
+      </c>
+    </row>
+    <row r="39" spans="4:8">
+      <c r="D39" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39">
+        <v>212.24268814826934</v>
+      </c>
+      <c r="F39">
+        <v>210.39356034603534</v>
+      </c>
+      <c r="G39">
+        <v>243.70298480529993</v>
+      </c>
+    </row>
+    <row r="41" spans="4:8">
+      <c r="H41">
+        <f>G39/G38</f>
+        <v>0.53596785697162963</v>
       </c>
     </row>
   </sheetData>
@@ -7902,15 +7963,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100478D9ACB663A0B44ABC718894EB3A5FF" ma:contentTypeVersion="12" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="9b81457e3208e76a02f6602a4efc0f0c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="45d80b71-d53a-4925-9636-d69011c62a0b" xmlns:ns3="853a583b-5a39-49db-b57b-0c8a2ee0f312" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6516941b06c58921cbe989d74b07aab8" ns2:_="" ns3:_="">
     <xsd:import namespace="45d80b71-d53a-4925-9636-d69011c62a0b"/>
@@ -8111,6 +8163,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -8123,15 +8184,30 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{330F525A-FEFE-4BB8-9F68-DD242C684B7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="45d80b71-d53a-4925-9636-d69011c62a0b"/>
+    <ds:schemaRef ds:uri="853a583b-5a39-49db-b57b-0c8a2ee0f312"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F91B0505-87C0-4533-9D1B-20F030974763}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{330F525A-FEFE-4BB8-9F68-DD242C684B7E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
